--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2A58C9-7ED9-4A26-A7E5-BC2524D6B0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCDDD75-0A3B-4310-A624-9984B56E07C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29460" yWindow="3030" windowWidth="21600" windowHeight="11235" tabRatio="948" firstSheet="6" activeTab="17" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="948" firstSheet="6" activeTab="10" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="11" r:id="rId1"/>
@@ -1733,14 +1733,13 @@
         <v>34</v>
       </c>
       <c r="F5" s="21">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G5" s="21">
-        <v>0.48549999999999999</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="H5" s="21">
-        <v>0.67633500000000002</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>34</v>
@@ -1759,14 +1758,13 @@
         <v>34</v>
       </c>
       <c r="F6" s="21">
-        <f>2.8-2.79</f>
-        <v>9.9999999999997868E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G6" s="21">
-        <v>0.48549999999999999</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H6" s="21">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>34</v>
@@ -7185,13 +7183,13 @@
         <v>34</v>
       </c>
       <c r="F5" s="21">
-        <v>-1.5900000000000001E-2</v>
+        <v>-1.7000000000000001E-2</v>
       </c>
       <c r="G5" s="21">
-        <v>0.50453999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="H5" s="21">
-        <v>0.62</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>34</v>
@@ -7210,13 +7208,13 @@
         <v>34</v>
       </c>
       <c r="F6" s="21">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G6" s="21">
-        <v>0.50453999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="H6" s="21">
-        <v>0.5</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>34</v>

--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SMILLER\TMW\Sharepoint\PM_Evl\sscMbody\2024\2409_VDGUP\Models_and_Files\Proj1\CAD_251201_New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCDDD75-0A3B-4310-A624-9984B56E07C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAD0190-91F4-45D0-8FD9-DCF502C15EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31050" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="948" firstSheet="6" activeTab="10" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="948" firstSheet="10" activeTab="19" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="11" r:id="rId1"/>
@@ -21,18 +21,18 @@
     <sheet name="Sedan_Hamba_Mac_f" sheetId="26" r:id="rId6"/>
     <sheet name="Sedan_Hamba_f" sheetId="12" r:id="rId7"/>
     <sheet name="Sedan_Hamba_r" sheetId="13" r:id="rId8"/>
-    <sheet name="SUV_Landy_TA2PR_f" sheetId="27" r:id="rId9"/>
-    <sheet name="SUV_Landy_DW_f" sheetId="30" r:id="rId10"/>
-    <sheet name="SUV_Landy_TA3_r" sheetId="29" r:id="rId11"/>
-    <sheet name="SUV_Landy_TA4Watts_r" sheetId="28" r:id="rId12"/>
-    <sheet name="Sedan_Hamba_TwistBeam_r" sheetId="22" r:id="rId13"/>
-    <sheet name="Achilles_f" sheetId="18" r:id="rId14"/>
-    <sheet name="Achilles_r" sheetId="19" r:id="rId15"/>
-    <sheet name="AchillesPush_f" sheetId="23" r:id="rId16"/>
-    <sheet name="AchillesPush_r" sheetId="24" r:id="rId17"/>
-    <sheet name="Achilles_DW_f" sheetId="20" r:id="rId18"/>
-    <sheet name="Achilles_DW_r" sheetId="21" r:id="rId19"/>
-    <sheet name="No_Spring" sheetId="15" r:id="rId20"/>
+    <sheet name="SUV_Landy_DW_f" sheetId="30" r:id="rId9"/>
+    <sheet name="SUV_Landy_TA3_r" sheetId="29" r:id="rId10"/>
+    <sheet name="SUV_Landy_TA4Watts_r" sheetId="28" r:id="rId11"/>
+    <sheet name="Sedan_Hamba_TwistBeam_r" sheetId="22" r:id="rId12"/>
+    <sheet name="Achilles_f" sheetId="18" r:id="rId13"/>
+    <sheet name="Achilles_r" sheetId="19" r:id="rId14"/>
+    <sheet name="AchillesPush_f" sheetId="23" r:id="rId15"/>
+    <sheet name="AchillesPush_r" sheetId="24" r:id="rId16"/>
+    <sheet name="Achilles_DW_f" sheetId="20" r:id="rId17"/>
+    <sheet name="Achilles_DW_r" sheetId="21" r:id="rId18"/>
+    <sheet name="No_Spring" sheetId="15" r:id="rId19"/>
+    <sheet name="None" sheetId="31" r:id="rId20"/>
     <sheet name="Bus_Makhulu_A1" sheetId="7" r:id="rId21"/>
     <sheet name="Bus_Makhulu_A2" sheetId="8" r:id="rId22"/>
     <sheet name="Bus_Makhulu_Axle3_A2" sheetId="16" r:id="rId23"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="46">
   <si>
     <t>Units</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Sedan_Hamba_Mac_Linear_A1</t>
   </si>
   <si>
-    <t>SUV_Landy_TA2PR_Linear_A1</t>
-  </si>
-  <si>
     <t>SUV_Landy_TA3_Linear_A2</t>
   </si>
   <si>
@@ -196,6 +193,9 @@
   </si>
   <si>
     <t>SUV_Landy_DW_Linear_A1</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -310,18 +310,12 @@
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="76">
     <dxf>
       <fill>
         <patternFill>
@@ -1384,17 +1378,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1403,248 +1397,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5813532A-0055-495A-92CC-4564E88CCAEA}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="6.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="19">
-        <v>-2.6557142857142869E-3</v>
-      </c>
-      <c r="G5" s="20">
-        <f>0.62-0.25</f>
-        <v>0.37</v>
-      </c>
-      <c r="H5" s="20">
-        <v>0.65</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="19">
-        <v>5.5166428571428582E-2</v>
-      </c>
-      <c r="G6" s="20">
-        <f>0.85-0.25</f>
-        <v>0.6</v>
-      </c>
-      <c r="H6" s="20">
-        <v>0.19</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="H18" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
-      <formula>"class"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2C4776-6841-4123-9B26-605C002DCD28}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -1703,7 +1455,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1732,14 +1484,14 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="21">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G5" s="21">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="H5" s="21">
-        <v>0.73899999999999999</v>
+      <c r="F5" s="22">
+        <v>2E-3</v>
+      </c>
+      <c r="G5" s="22">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="H5" s="22">
+        <v>0.80200000000000005</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>34</v>
@@ -1757,14 +1509,14 @@
       <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="21">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="G6" s="21">
+      <c r="F6" s="22">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="G6" s="22">
         <v>0.54300000000000004</v>
       </c>
-      <c r="H6" s="21">
-        <v>0.53</v>
+      <c r="H6" s="22">
+        <v>0.57299999999999995</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>34</v>
@@ -1866,17 +1618,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="45" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="44" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1884,7 +1636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E8D496-DF59-409E-A48B-66FD969D114E}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -1943,7 +1695,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2108,17 +1860,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2126,7 +1878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87769F25-0D9B-4A5D-A483-AACA58CC7443}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -2348,17 +2100,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2366,7 +2118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07675E27-4F23-45DF-B815-2A58E614CCF5}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -2589,17 +2341,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2607,7 +2359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6819F1-CEED-4A60-B116-BA176ED148CB}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -2830,17 +2582,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="34" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2848,7 +2600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F153D3AE-46C7-4F34-AC73-2C191830CCFC}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -3071,17 +2823,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3089,7 +2841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A666DF0F-6AE0-4055-9B98-97F7038D423B}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -3312,17 +3064,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3330,7 +3082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AF275A-B12B-4AB2-BD05-ACD618B3C10D}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -3554,17 +3306,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3572,7 +3324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0AF0D6-3E7E-4BDA-8817-856CC0C9A380}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
@@ -3796,17 +3548,158 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE32C537-D3E6-4C00-9A05-E96827E0CC18}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="5" width="11.140625" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="6.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="16"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="16"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="H14" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4 A9:B12">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A14">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4036,17 +3929,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="73" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="71" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4055,7 +3948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE32C537-D3E6-4C00-9A05-E96827E0CC18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4047D148-8044-4048-89F3-739259E56ACA}">
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
@@ -4113,7 +4006,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -4127,7 +4020,7 @@
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
       <c r="H4" s="11" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -4182,12 +4075,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A9:B12">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4419,17 +4312,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4661,17 +4554,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4903,17 +4796,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5145,17 +5038,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5387,17 +5280,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5630,17 +5523,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5870,17 +5763,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="70" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="69" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6110,17 +6003,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="67" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="66" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="65" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6350,17 +6243,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="64" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="63" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="62" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6592,17 +6485,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="61" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="60" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="59" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6834,17 +6727,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="56" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7076,17 +6969,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="55" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="54" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7095,7 +6988,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D925D91A-EF8A-4D90-95BF-22FD4E1F34B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5813532A-0055-495A-92CC-4564E88CCAEA}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -7153,7 +7046,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -7182,14 +7075,15 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="21">
-        <v>-1.7000000000000001E-2</v>
-      </c>
-      <c r="G5" s="21">
-        <v>0.48399999999999999</v>
-      </c>
-      <c r="H5" s="21">
-        <v>0.65500000000000003</v>
+      <c r="F5" s="19">
+        <v>-2.6557142857142869E-3</v>
+      </c>
+      <c r="G5" s="20">
+        <f>0.62-0.25</f>
+        <v>0.37</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0.65</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>34</v>
@@ -7207,14 +7101,15 @@
       <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="21">
-        <v>-0.02</v>
-      </c>
-      <c r="G6" s="21">
-        <v>0.49</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0.49199999999999999</v>
+      <c r="F6" s="19">
+        <v>5.5166428571428582E-2</v>
+      </c>
+      <c r="G6" s="20">
+        <f>0.85-0.25</f>
+        <v>0.6</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0.19</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>34</v>
@@ -7316,17 +7211,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAD0190-91F4-45D0-8FD9-DCF502C15EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F33540C-1A74-4207-866F-4F414ADFA2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="948" firstSheet="10" activeTab="19" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="948" firstSheet="8" activeTab="8" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="11" r:id="rId1"/>
@@ -1776,7 +1776,8 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="15">
-        <v>52000</v>
+        <f>52000*1.5</f>
+        <v>78000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1793,7 +1794,8 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="6">
-        <v>0.1</v>
+        <f>0.1/1.5</f>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4075,12 +4077,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A9:B12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4312,17 +4314,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4554,17 +4556,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4796,17 +4798,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5038,17 +5040,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5280,17 +5282,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5523,17 +5525,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7127,7 +7129,8 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="15">
-        <v>52000</v>
+        <f>52000*1.5</f>
+        <v>78000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -7144,7 +7147,8 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="6">
-        <v>0.1</v>
+        <f>0.1/1.5</f>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">

--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F33540C-1A74-4207-866F-4F414ADFA2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED8D07E-E201-4805-BE28-43202B9A641A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="948" firstSheet="8" activeTab="8" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12495" windowHeight="15585" tabRatio="948" firstSheet="9" activeTab="9" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="11" r:id="rId1"/>

--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_Linear.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAD0190-91F4-45D0-8FD9-DCF502C15EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED8D07E-E201-4805-BE28-43202B9A641A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="948" firstSheet="10" activeTab="19" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12495" windowHeight="15585" tabRatio="948" firstSheet="9" activeTab="9" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="11" r:id="rId1"/>
@@ -1776,7 +1776,8 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="15">
-        <v>52000</v>
+        <f>52000*1.5</f>
+        <v>78000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1793,7 +1794,8 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="6">
-        <v>0.1</v>
+        <f>0.1/1.5</f>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -4075,12 +4077,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A9:B12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:A14">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4312,17 +4314,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="17" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4554,17 +4556,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4796,17 +4798,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5038,17 +5040,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4 A5:B8 A13:B16">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5280,17 +5282,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5523,17 +5525,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A9">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:B16">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7127,7 +7129,8 @@
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="15">
-        <v>52000</v>
+        <f>52000*1.5</f>
+        <v>78000</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -7144,7 +7147,8 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="6">
-        <v>0.1</v>
+        <f>0.1/1.5</f>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
